--- a/Result/profitability/2606.xlsx
+++ b/Result/profitability/2606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.22</v>
       </c>
       <c r="M2" t="n">
-        <v>1.45375</v>
+        <v>1.51625</v>
       </c>
       <c r="N2" t="n">
-        <v>34.1575</v>
+        <v>33.65375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.63125</v>
+        <v>1.7875</v>
       </c>
       <c r="N3" t="n">
-        <v>37.3125</v>
+        <v>38.075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9225</v>
+        <v>2.18125</v>
       </c>
       <c r="N4" t="n">
-        <v>41.77625</v>
+        <v>43.85375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.27</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1725</v>
+        <v>2.36875</v>
       </c>
       <c r="N5" t="n">
-        <v>46.75625</v>
+        <v>48.31125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.26875</v>
+        <v>2.34625</v>
       </c>
       <c r="N6" t="n">
-        <v>49.53375</v>
+        <v>49.5425</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>2.23</v>
+        <v>2.32875</v>
       </c>
       <c r="N7" t="n">
-        <v>51.1475</v>
+        <v>51.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>2.28</v>
+        <v>2.42625</v>
       </c>
       <c r="N8" t="n">
-        <v>52.24375</v>
+        <v>52.66125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5033</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3260</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1773</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1557</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>484</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2041</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1976</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.34375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.91999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1047678795483062</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.038961038961039</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.546093064091308</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
